--- a/manuscript_material/source_data/Source_Data_ED_Fig5.xlsx
+++ b/manuscript_material/source_data/Source_Data_ED_Fig5.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a_token_overhead" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_direct_interface_use" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a_input_token_ratio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_direct_galaxy_api_calls" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +420,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>configuration</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -430,7 +430,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>median_ratio</t>
+          <t>median_input_token_ratio</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>galaxy_runs</t>
+          <t>galaxy_condition_runs</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -740,7 +740,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Copy the provided input history</t>
+          <t>Copy the provided analysis history</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/manuscript_material/source_data/Source_Data_ED_Fig5.xlsx
+++ b/manuscript_material/source_data/Source_Data_ED_Fig5.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a_input_token_ratio" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_direct_galaxy_api_calls" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a_divergence_by_model_configura" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_iwc_split_galaxy_sets" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -425,22 +425,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>benchmark</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>median_input_token_ratio</t>
+          <t>divergence_mechanism</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ci_low</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ci_high</t>
+          <t>scored_incorrect_replicate_runs</t>
         </is>
       </c>
     </row>
@@ -452,17 +447,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>3.86</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Domain convention or definition applied differently</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5.81</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -473,38 +467,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3.14</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Hand-written method instead of the library method</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1.66</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Domain convention or definition applied differently</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3.55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -515,17 +507,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>5.03</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Hand-written method instead of the library method</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6.07</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -536,17 +527,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>6.63</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Different software version installed</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8.58</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -557,38 +547,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2.77</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Error in the final step (sorting, counting, units)</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>7.63</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Galaxy interface trap (silent default, output semantics or job not dispatched)</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>6.27</v>
-      </c>
-      <c r="E8" t="n">
-        <v>13.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -599,17 +587,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>5.73</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Domain convention or definition applied differently</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8.380000000000001</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -620,80 +607,376 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2.41</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hand-written method instead of the library method</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5.04</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>All three shared configurations</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5.28</v>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Different software version installed</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="E11" t="n">
-        <v>7.07</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>All three shared configurations</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>4.83</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Domain convention or definition applied differently</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5.87</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>All three shared configurations</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1.88</v>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Error in the final step (sorting, counting, units)</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4.7</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Domain convention or definition applied differently</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hand-written method instead of the library method</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Answer retrieved from benchmark source files</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Domain convention or definition applied differently</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>No answer submitted</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Galaxy interface trap (silent default, output semantics or job not dispatched)</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Answer retrieved from benchmark source files</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Domain convention or definition applied differently</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Error in the final step (sorting, counting, units)</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Hand-written method instead of the library method</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Open-ended code condition</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No answer submitted</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Domain convention or definition applied differently</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Error in the final step (sorting, counting, units)</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hand-written method instead of the library method</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Galaxy condition</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Galaxy interface trap (silent default, output semantics or job not dispatched)</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -707,307 +990,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>operation</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>benchmark</t>
+          <t>task</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>runs</t>
+          <t>replicate_runs</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>galaxy_condition_runs</t>
+          <t>within_set_range</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>cause</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Copy the provided analysis history</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>537</v>
+          <t>Mitogenome assembly</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.000; 1.000; 0.994</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>600</v>
-      </c>
-      <c r="E2" t="n">
-        <v>89.5</v>
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Replicate run 1 submitted a nuclear contig without checking mitochondrial identity (0.000).</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Download output files</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>580</v>
+          <t>Peptide verification</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.982; 0.908; 0.982</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>600</v>
-      </c>
-      <c r="E3" t="n">
-        <v>96.7</v>
+        <v>0.074</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Replicate run 2 used the older PepQuery 1.6.2 wrapper (0.908); runs 1 and 3 used PepQuery2 2.0.2.</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Read a tool's parameter description</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>182</v>
+          <t>Host-read removal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.273; 1.000; 0.273</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>600</v>
-      </c>
-      <c r="E4" t="n">
-        <v>30.3</v>
+        <v>0.727</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Score conflict in runs 1 and 3: correct BWA-MEM output scored against the Bowtie2 reference (0.273; run record 0.9999 and 1.0).</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Check job status</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>92</v>
+          <t>Peptide verification</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.982; 0.868; 0.900</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>600</v>
-      </c>
-      <c r="E5" t="n">
-        <v>15.3</v>
+        <v>0.115</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Run 2 used PepQuery 1.6.2 (0.868); run 3 used PepQuery2, but its unrestricted- modification step searched no protein sequences (0.900).</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Submit a job directly, bypassing checks</t>
+          <t>GPT-5.6 Sol</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>22</v>
+          <t>Peptide verification</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.982; 0.982; 0.908</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>600</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Download output files</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>234</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E7" t="n">
-        <v>19.7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Read a tool's parameter description</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>193</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E8" t="n">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Check job status</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>237</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E9" t="n">
-        <v>19.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Submit a job directly, bypassing checks</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>209</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E10" t="n">
-        <v>17.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Download output files</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>73</v>
-      </c>
-      <c r="D11" t="n">
-        <v>120</v>
-      </c>
-      <c r="E11" t="n">
-        <v>60.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Read a tool's parameter description</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>24</v>
-      </c>
-      <c r="D12" t="n">
-        <v>120</v>
-      </c>
-      <c r="E12" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Check job status</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>57</v>
-      </c>
-      <c r="D13" t="n">
-        <v>120</v>
-      </c>
-      <c r="E13" t="n">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Submit a job directly, bypassing checks</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>37</v>
-      </c>
-      <c r="D14" t="n">
-        <v>120</v>
-      </c>
-      <c r="E14" t="n">
-        <v>30.8</v>
+        <v>0.074</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Replicate run 3 used the older PepQuery 1.6.2 wrapper (0.908).</t>
+        </is>
       </c>
     </row>
   </sheetData>
